--- a/data/trans_orig/Q5404-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q5404-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de manejar dinero en 2007</t>
+          <t>Población según si es capaz de manejar dinero en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,97 +733,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1169</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1733</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5774</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2,98%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>14,72%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1169</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6706</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,98%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>6370</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>17,09%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1169</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5282</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6126</t>
+          <t>5621</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5173</t>
+          <t>5477</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>889</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7359</t>
+          <t>7284</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29260</t>
+          <t>29765</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>32202</t>
+          <t>31483</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>65286</t>
+          <t>65748</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>73685</t>
+          <t>73595</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9874</t>
+          <t>9171</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>902</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>2126</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13242</t>
+          <t>12792</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>979</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9166</t>
+          <t>9091</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>898</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9309</t>
+          <t>8567</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56780</t>
+          <t>57483</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>84876</t>
+          <t>84284</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>94904</t>
+          <t>94660</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>146517</t>
+          <t>146140</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>159837</t>
+          <t>159655</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,04%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1167</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10490</t>
+          <t>11167</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1143</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11281</t>
+          <t>11372</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5063</t>
+          <t>5631</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>6528</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>962</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8277</t>
+          <t>8564</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>45877</t>
+          <t>45309</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>70546</t>
+          <t>69859</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>81223</t>
+          <t>80326</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>119526</t>
+          <t>119117</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>131152</t>
+          <t>131153</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4062</t>
+          <t>4177</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6160</t>
+          <t>5341</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6843</t>
+          <t>7038</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>828</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6986</t>
+          <t>7476</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9898</t>
+          <t>9896</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2999</t>
+          <t>3120</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13522</t>
+          <t>13473</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>47271</t>
+          <t>46462</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>54261</t>
+          <t>54277</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>62645</t>
+          <t>62430</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>72158</t>
+          <t>72132</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>113604</t>
+          <t>113613</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>124767</t>
+          <t>124760</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4468</t>
+          <t>4796</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9250</t>
+          <t>9399</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1829</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10899</t>
+          <t>10756</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1674</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8975</t>
+          <t>8440</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1113</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9451</t>
+          <t>10591</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3888</t>
+          <t>4147</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>14850</t>
+          <t>14996</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,24%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18939</t>
+          <t>19840</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27004</t>
+          <t>27521</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27288</t>
+          <t>26572</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>37317</t>
+          <t>37183</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>49749</t>
+          <t>50097</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>62757</t>
+          <t>62752</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>88,89%</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4323</t>
+          <t>4321</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1147</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8939</t>
+          <t>9594</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>1356</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10363</t>
+          <t>11398</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5768</t>
+          <t>5959</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5848</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>938</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8896</t>
+          <t>8259</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>40382</t>
+          <t>39254</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>47196</t>
+          <t>46338</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>59226</t>
+          <t>59315</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>69123</t>
+          <t>68903</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>102721</t>
+          <t>102405</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>114467</t>
+          <t>114062</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,07%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>813</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7196</t>
+          <t>7285</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1789</t>
+          <t>1813</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10692</t>
+          <t>11121</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3554</t>
+          <t>3570</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>14310</t>
+          <t>13950</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>891</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9002</t>
+          <t>8893</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7513</t>
+          <t>7753</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2396</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>11362</t>
+          <t>11962</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>93689</t>
+          <t>94487</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>103331</t>
+          <t>103241</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>103508</t>
+          <t>103303</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>114168</t>
+          <t>114202</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>200929</t>
+          <t>202333</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>215513</t>
+          <t>215875</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,78%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>752</t>
+          <t>750</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>7158</t>
+          <t>7259</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2094</t>
+          <t>2342</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>12824</t>
+          <t>13647</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4219</t>
+          <t>4097</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>16440</t>
+          <t>17455</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>1956</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>11867</t>
+          <t>11502</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>8352</t>
+          <t>8452</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>23893</t>
+          <t>24223</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>12491</t>
+          <t>12912</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>31180</t>
+          <t>30907</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,66%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>96639</t>
+          <t>97191</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>107981</t>
+          <t>107684</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>122562</t>
+          <t>121600</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>140694</t>
+          <t>139877</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>224451</t>
+          <t>221915</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>245570</t>
+          <t>244613</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,27%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5392</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>18015</t>
+          <t>19218</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>19218</t>
+          <t>19259</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>41045</t>
+          <t>40464</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>27873</t>
+          <t>28782</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>53769</t>
+          <t>55118</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>13916</t>
+          <t>13308</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>31602</t>
+          <t>29910</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>24032</t>
+          <t>24356</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>47431</t>
+          <t>47509</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>41916</t>
+          <t>42763</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>69174</t>
+          <t>70900</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>457783</t>
+          <t>459469</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>480232</t>
+          <t>480326</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>597619</t>
+          <t>597520</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>627669</t>
+          <t>628825</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1064244</t>
+          <t>1062788</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1102137</t>
+          <t>1102062</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,45%</t>
         </is>
       </c>
     </row>
@@ -4878,7 +4878,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de manejar dinero en 2012</t>
+          <t>Población según si es capaz de manejar dinero en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6032</t>
+          <t>6164</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5108,12 +5108,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1090</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8860</t>
+          <t>9139</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10761</t>
+          <t>12006</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>12,89%</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4384</t>
+          <t>5407</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4157</t>
+          <t>4121</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15678</t>
+          <t>14966</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4787</t>
+          <t>4121</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17934</t>
+          <t>16448</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37332</t>
+          <t>36313</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43386</t>
+          <t>43364</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30139</t>
+          <t>29898</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>42493</t>
+          <t>42592</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>70349</t>
+          <t>70546</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>84480</t>
+          <t>84496</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,68%</t>
         </is>
       </c>
     </row>
@@ -5529,12 +5529,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15070</t>
+          <t>13766</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2259</t>
+          <t>2293</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14618</t>
+          <t>14630</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5747</t>
+          <t>5754</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>24065</t>
+          <t>21015</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5619,7 +5619,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>11,59%</t>
         </is>
       </c>
     </row>
@@ -5642,12 +5642,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15170</t>
+          <t>14195</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5657,12 +5657,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7460</t>
+          <t>7256</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20619</t>
+          <t>21189</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>10650</t>
+          <t>10835</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>29344</t>
+          <t>29706</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5727,12 +5727,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,39%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>58821</t>
+          <t>58085</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>74653</t>
+          <t>74148</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>72799</t>
+          <t>72670</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>89944</t>
+          <t>90042</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>136441</t>
+          <t>138558</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>160838</t>
+          <t>161165</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,9%</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10093</t>
+          <t>10311</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4312</t>
+          <t>4337</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15199</t>
+          <t>15357</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7634</t>
+          <t>7602</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>21856</t>
+          <t>22114</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,3%</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>4273</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6133,12 +6133,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4227</t>
+          <t>4126</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14736</t>
+          <t>15540</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5169</t>
+          <t>4285</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17505</t>
+          <t>17032</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,55%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>44478</t>
+          <t>44247</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>53706</t>
+          <t>52833</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>54861</t>
+          <t>54157</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>69401</t>
+          <t>68964</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>102381</t>
+          <t>102576</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>119862</t>
+          <t>119739</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,23%</t>
         </is>
       </c>
     </row>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8258</t>
+          <t>9207</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8831</t>
+          <t>8777</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12725</t>
+          <t>12950</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6554,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3298</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14526</t>
+          <t>14304</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5334</t>
+          <t>4561</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17556</t>
+          <t>17065</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10036</t>
+          <t>10794</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>26896</t>
+          <t>27009</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,05%</t>
         </is>
       </c>
     </row>
@@ -6667,12 +6667,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45726</t>
+          <t>45909</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>58463</t>
+          <t>58501</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>65376</t>
+          <t>64656</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>78939</t>
+          <t>78814</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>116418</t>
+          <t>115219</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>134423</t>
+          <t>133843</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6752,12 +6752,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,47%</t>
         </is>
       </c>
     </row>
@@ -6902,7 +6902,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5727</t>
+          <t>5522</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>2869</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12112</t>
+          <t>12325</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3106</t>
+          <t>3065</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13799</t>
+          <t>14375</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,64%</t>
         </is>
       </c>
     </row>
@@ -7010,12 +7010,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>993</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8791</t>
+          <t>7896</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6485</t>
+          <t>6799</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2115</t>
+          <t>2211</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>12003</t>
+          <t>12122</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7095,12 +7095,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,88%</t>
         </is>
       </c>
     </row>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22347</t>
+          <t>22169</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30501</t>
+          <t>30481</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>34709</t>
+          <t>35483</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>45834</t>
+          <t>45733</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>61305</t>
+          <t>60636</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>74311</t>
+          <t>74406</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7208,12 +7208,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,33%</t>
         </is>
       </c>
     </row>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7476</t>
+          <t>7156</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>2128</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11826</t>
+          <t>10778</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3199</t>
+          <t>3229</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>15083</t>
+          <t>14026</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>11,5%</t>
         </is>
       </c>
     </row>
@@ -7471,7 +7471,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6485</t>
+          <t>7180</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4198</t>
+          <t>4109</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14904</t>
+          <t>14833</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5315</t>
+          <t>5255</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>18624</t>
+          <t>17794</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7551,12 +7551,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>14,59%</t>
         </is>
       </c>
     </row>
@@ -7579,12 +7579,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>42078</t>
+          <t>42080</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>50677</t>
+          <t>50665</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>49015</t>
+          <t>49121</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>62693</t>
+          <t>62644</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>69,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>94187</t>
+          <t>95270</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>111127</t>
+          <t>111179</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,15%</t>
         </is>
       </c>
     </row>
@@ -7809,12 +7809,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>958</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8288</t>
+          <t>8131</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7824,12 +7824,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2973</t>
+          <t>2989</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>14673</t>
+          <t>13886</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4849</t>
+          <t>4997</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>17509</t>
+          <t>18254</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -7922,12 +7922,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>956</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8013</t>
+          <t>8189</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>8371</t>
+          <t>9389</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>24593</t>
+          <t>24676</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7972,12 +7972,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>11353</t>
+          <t>11512</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>28930</t>
+          <t>28571</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -8035,12 +8035,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>99343</t>
+          <t>100042</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>110154</t>
+          <t>110094</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>109357</t>
+          <t>109429</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>127865</t>
+          <t>126983</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>213908</t>
+          <t>213074</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>234913</t>
+          <t>234443</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8120,12 +8120,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,22%</t>
         </is>
       </c>
     </row>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5316</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8285,7 +8285,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>2191</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>12196</t>
+          <t>12964</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8315,12 +8315,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>2297</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>14489</t>
+          <t>13658</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8350,12 +8350,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -8378,12 +8378,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2184</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>15860</t>
+          <t>15393</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8393,12 +8393,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>5380</t>
+          <t>4613</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>18893</t>
+          <t>18128</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8428,12 +8428,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>10162</t>
+          <t>9912</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>28576</t>
+          <t>28499</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8463,12 +8463,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -8491,12 +8491,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>103730</t>
+          <t>104139</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>117450</t>
+          <t>117325</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8506,12 +8506,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>138462</t>
+          <t>139543</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>155539</t>
+          <t>156432</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>249624</t>
+          <t>248783</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>269796</t>
+          <t>269866</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,63%</t>
         </is>
       </c>
     </row>
@@ -8721,12 +8721,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>14513</t>
+          <t>13843</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>35101</t>
+          <t>33816</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>33631</t>
+          <t>34137</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>61169</t>
+          <t>60379</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>54235</t>
+          <t>54167</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>87573</t>
+          <t>87626</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8811,7 +8811,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -8834,12 +8834,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>20052</t>
+          <t>19699</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>45463</t>
+          <t>44532</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8849,12 +8849,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>60104</t>
+          <t>60606</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>93293</t>
+          <t>95705</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>86442</t>
+          <t>87021</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>127076</t>
+          <t>128747</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8919,12 +8919,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -8947,12 +8947,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>488260</t>
+          <t>490400</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>519724</t>
+          <t>520596</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8962,12 +8962,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>597793</t>
+          <t>598491</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>641081</t>
+          <t>639661</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8997,12 +8997,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1103585</t>
+          <t>1098264</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1153991</t>
+          <t>1152995</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,51%</t>
         </is>
       </c>
     </row>
@@ -9218,7 +9218,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de manejar dinero en 2016</t>
+          <t>Población según si es capaz de manejar dinero en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9413,12 +9413,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>782</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6482</t>
+          <t>6673</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9577</t>
+          <t>9137</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12126</t>
+          <t>12274</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,9%</t>
         </is>
       </c>
     </row>
@@ -9526,12 +9526,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1597</t>
+          <t>1596</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8584</t>
+          <t>9205</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2194</t>
+          <t>2453</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13447</t>
+          <t>14410</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9596,12 +9596,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4882</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18758</t>
+          <t>19358</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,93%</t>
         </is>
       </c>
     </row>
@@ -9639,12 +9639,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27369</t>
+          <t>26153</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35692</t>
+          <t>35649</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>32178</t>
+          <t>32314</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>44701</t>
+          <t>44736</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>63345</t>
+          <t>62524</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>78752</t>
+          <t>77736</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>88,05%</t>
         </is>
       </c>
     </row>
@@ -9869,12 +9869,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1838</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10545</t>
+          <t>10721</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9939,12 +9939,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10444</t>
+          <t>10814</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9959,7 +9959,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -9982,12 +9982,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>732</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7105</t>
+          <t>6735</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2656</t>
+          <t>2671</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14643</t>
+          <t>14863</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10052,12 +10052,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4703</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>17818</t>
+          <t>17166</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -10095,12 +10095,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>80190</t>
+          <t>80560</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>86576</t>
+          <t>86563</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>95624</t>
+          <t>94500</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>109996</t>
+          <t>109956</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>180383</t>
+          <t>179788</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>195739</t>
+          <t>195829</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,69%</t>
         </is>
       </c>
     </row>
@@ -10325,12 +10325,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1667</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10340,12 +10340,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1227</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12285</t>
+          <t>12592</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10395,12 +10395,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1239</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13738</t>
+          <t>11728</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10410,12 +10410,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -10438,12 +10438,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>860</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8466</t>
+          <t>9097</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10478,7 +10478,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7606</t>
+          <t>8562</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10493,7 +10493,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10508,12 +10508,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2646</t>
+          <t>2191</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13690</t>
+          <t>12086</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10523,12 +10523,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>55080</t>
+          <t>54449</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>62666</t>
+          <t>62686</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>64427</t>
+          <t>64707</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>77409</t>
+          <t>77420</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10621,12 +10621,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>123692</t>
+          <t>123816</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>138468</t>
+          <t>138297</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10636,12 +10636,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,41%</t>
         </is>
       </c>
     </row>
@@ -10786,7 +10786,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4526</t>
+          <t>4194</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10801,7 +10801,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11692</t>
+          <t>11134</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10836,7 +10836,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>855</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12679</t>
+          <t>13784</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10871,7 +10871,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -10894,12 +10894,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>810</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7080</t>
+          <t>7205</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10929,12 +10929,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9558</t>
+          <t>8838</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2333</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12754</t>
+          <t>12644</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,09%</t>
         </is>
       </c>
     </row>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>56231</t>
+          <t>56488</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>63776</t>
+          <t>63855</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11042,12 +11042,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>76318</t>
+          <t>76867</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>89072</t>
+          <t>89209</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>136631</t>
+          <t>136498</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>151045</t>
+          <t>151484</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,93%</t>
         </is>
       </c>
     </row>
@@ -11237,97 +11237,97 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>909</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1676</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>4710</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>3,98%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>9,32%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>909</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>4704</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>4298</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>9,31%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>909</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>5190</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1676</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11365,12 +11365,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11385,12 +11385,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11700</t>
+          <t>12135</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2130</t>
+          <t>1889</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>12030</t>
+          <t>11262</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,16%</t>
         </is>
       </c>
     </row>
@@ -11463,12 +11463,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>40404</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42080</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11478,12 +11478,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11498,12 +11498,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>37866</t>
+          <t>38280</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>48185</t>
+          <t>48284</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>75,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>79701</t>
+          <t>80279</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>89846</t>
+          <t>90484</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,7%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1647</t>
+          <t>1596</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9541</t>
+          <t>8954</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13115</t>
+          <t>13423</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4722</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>18631</t>
+          <t>18825</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,25%</t>
         </is>
       </c>
     </row>
@@ -11806,12 +11806,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>790</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6582</t>
+          <t>5863</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11846,7 +11846,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8958</t>
+          <t>8616</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11861,7 +11861,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1656</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11290</t>
+          <t>11015</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -11919,12 +11919,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>36213</t>
+          <t>36086</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>45108</t>
+          <t>45139</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11934,12 +11934,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11954,12 +11954,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>52130</t>
+          <t>51763</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>64787</t>
+          <t>64760</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11969,12 +11969,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11989,12 +11989,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>91964</t>
+          <t>92041</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>107512</t>
+          <t>106797</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12004,12 +12004,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,2%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>877</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7371</t>
+          <t>7216</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>2544</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>14742</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4459</t>
+          <t>4547</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>17990</t>
+          <t>18571</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -12262,12 +12262,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1766</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10286</t>
+          <t>10690</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>9191</t>
+          <t>8089</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>25574</t>
+          <t>23957</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>12981</t>
+          <t>13128</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>32035</t>
+          <t>31428</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12347,12 +12347,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -12375,12 +12375,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>98278</t>
+          <t>97947</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>108599</t>
+          <t>108543</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12390,12 +12390,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>115073</t>
+          <t>113558</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>133853</t>
+          <t>133906</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>216765</t>
+          <t>216951</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>239238</t>
+          <t>238634</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12460,12 +12460,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>91,85%</t>
         </is>
       </c>
     </row>
@@ -12605,97 +12605,97 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="R32" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>2364</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>2098</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4458</t>
+          <t>4751</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12738,7 +12738,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12753,12 +12753,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2302</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>13088</t>
+          <t>13360</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12773,7 +12773,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2683</t>
+          <t>2393</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>15126</t>
+          <t>13986</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -12831,7 +12831,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>129710</t>
+          <t>129417</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -12846,7 +12846,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -12866,12 +12866,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>163209</t>
+          <t>162937</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>173980</t>
+          <t>173995</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12881,7 +12881,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -12901,12 +12901,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>295339</t>
+          <t>296479</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>307782</t>
+          <t>308072</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12916,12 +12916,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>5304</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>17152</t>
+          <t>17202</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>18963</t>
+          <t>18178</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>43905</t>
+          <t>42735</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>27935</t>
+          <t>26846</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>55570</t>
+          <t>54224</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>13451</t>
+          <t>13687</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>31304</t>
+          <t>30963</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>35064</t>
+          <t>35940</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>64272</t>
+          <t>67382</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13244,12 +13244,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>54949</t>
+          <t>53558</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>88027</t>
+          <t>88741</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13259,12 +13259,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -13287,12 +13287,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>549089</t>
+          <t>549165</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>569142</t>
+          <t>568723</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13322,12 +13322,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>680141</t>
+          <t>679022</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>718071</t>
+          <t>717207</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1238855</t>
+          <t>1240146</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1281396</t>
+          <t>1282104</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13372,12 +13372,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,63%</t>
         </is>
       </c>
     </row>
@@ -13558,7 +13558,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de manejar dinero en 2023</t>
+          <t>Población según si es capaz de manejar dinero en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13753,12 +13753,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13768,12 +13768,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13788,12 +13788,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t>6746</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13803,12 +13803,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13823,12 +13823,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1137</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6529</t>
+          <t>6536</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13838,12 +13838,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -13866,12 +13866,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2309</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10159</t>
+          <t>10329</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13881,12 +13881,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13901,12 +13901,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9363</t>
+          <t>9732</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18431</t>
+          <t>18872</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13916,12 +13916,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13936,12 +13936,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13261</t>
+          <t>12939</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>25419</t>
+          <t>25869</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13951,12 +13951,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,68%</t>
         </is>
       </c>
     </row>
@@ -13979,12 +13979,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>45742</t>
+          <t>45572</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53592</t>
+          <t>53588</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13994,12 +13994,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -14014,12 +14014,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>41151</t>
+          <t>41093</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>50955</t>
+          <t>51291</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -14029,12 +14029,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>64,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>90425</t>
+          <t>89624</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>103035</t>
+          <t>103420</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -14064,12 +14064,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,68%</t>
         </is>
       </c>
     </row>
@@ -14214,7 +14214,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5696</t>
+          <t>5915</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -14229,7 +14229,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6553</t>
+          <t>6357</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17080</t>
+          <t>17665</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -14259,12 +14259,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14279,12 +14279,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7871</t>
+          <t>7712</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>19506</t>
+          <t>19626</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14294,12 +14294,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -14322,12 +14322,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>2543</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11498</t>
+          <t>10495</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -14337,12 +14337,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14357,12 +14357,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11377</t>
+          <t>11049</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22425</t>
+          <t>22439</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -14372,12 +14372,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14392,12 +14392,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>15548</t>
+          <t>15057</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>29161</t>
+          <t>29304</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14407,12 +14407,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,97%</t>
         </is>
       </c>
     </row>
@@ -14435,12 +14435,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>67352</t>
+          <t>67659</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>77332</t>
+          <t>77257</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14450,12 +14450,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14470,12 +14470,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>95119</t>
+          <t>94534</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>108755</t>
+          <t>108874</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14485,12 +14485,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14505,12 +14505,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>166779</t>
+          <t>165484</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>183297</t>
+          <t>183366</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14520,12 +14520,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,44%</t>
         </is>
       </c>
     </row>
@@ -14665,12 +14665,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1648</t>
+          <t>1756</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8089</t>
+          <t>8322</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14700,12 +14700,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>1745</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7539</t>
+          <t>7406</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14715,12 +14715,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14735,12 +14735,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4525</t>
+          <t>4787</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12931</t>
+          <t>12770</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -14778,12 +14778,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>1124</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6660</t>
+          <t>6599</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14793,12 +14793,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14813,12 +14813,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4453</t>
+          <t>4657</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11994</t>
+          <t>12648</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14828,12 +14828,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14848,12 +14848,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7138</t>
+          <t>7236</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16138</t>
+          <t>16667</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14863,12 +14863,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,36%</t>
         </is>
       </c>
     </row>
@@ -14891,12 +14891,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>61571</t>
+          <t>61523</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>69731</t>
+          <t>69374</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14906,12 +14906,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14926,12 +14926,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>70686</t>
+          <t>69945</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>79960</t>
+          <t>79979</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14941,12 +14941,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14961,12 +14961,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>135056</t>
+          <t>135368</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>147066</t>
+          <t>147439</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14976,12 +14976,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,63%</t>
         </is>
       </c>
     </row>
@@ -15126,7 +15126,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3434</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -15156,12 +15156,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2387</t>
+          <t>2355</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7424</t>
+          <t>8081</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -15171,12 +15171,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -15191,12 +15191,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2785</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8321</t>
+          <t>8030</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -15206,12 +15206,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -15234,12 +15234,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8815</t>
+          <t>8681</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15269,12 +15269,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3747</t>
+          <t>3395</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10091</t>
+          <t>9825</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15284,12 +15284,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15304,12 +15304,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6594</t>
+          <t>6918</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15397</t>
+          <t>16230</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15319,12 +15319,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -15347,12 +15347,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>65407</t>
+          <t>65573</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>72436</t>
+          <t>72509</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15382,12 +15382,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>88716</t>
+          <t>87993</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>96201</t>
+          <t>96336</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15397,12 +15397,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15417,12 +15417,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>157341</t>
+          <t>156904</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>167030</t>
+          <t>167009</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,67%</t>
         </is>
       </c>
     </row>
@@ -15577,12 +15577,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15592,12 +15592,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3464</t>
+          <t>3322</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15632,7 +15632,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15647,12 +15647,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>349</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3584</t>
+          <t>3236</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15667,7 +15667,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -15690,12 +15690,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1908</t>
+          <t>1954</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7009</t>
+          <t>7661</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -15705,12 +15705,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15725,12 +15725,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4887</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11649</t>
+          <t>11302</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15740,12 +15740,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15760,12 +15760,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>8595</t>
+          <t>8525</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>16481</t>
+          <t>16361</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15775,12 +15775,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,39%</t>
         </is>
       </c>
     </row>
@@ -15803,12 +15803,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27807</t>
+          <t>27155</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32908</t>
+          <t>32862</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15818,12 +15818,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15838,12 +15838,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>46159</t>
+          <t>46075</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>53196</t>
+          <t>53050</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15853,12 +15853,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15873,12 +15873,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>76096</t>
+          <t>76197</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>84459</t>
+          <t>84526</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15888,12 +15888,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,86%</t>
         </is>
       </c>
     </row>
@@ -16033,12 +16033,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>717</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4311</t>
+          <t>4476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -16068,12 +16068,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3153</t>
+          <t>2815</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8727</t>
+          <t>8061</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -16083,12 +16083,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4374</t>
+          <t>4421</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10529</t>
+          <t>10740</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -16118,12 +16118,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -16146,12 +16146,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>848</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5665</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -16161,12 +16161,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -16181,12 +16181,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2579</t>
+          <t>2739</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7499</t>
+          <t>7995</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -16196,12 +16196,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -16216,12 +16216,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4817</t>
+          <t>4586</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11311</t>
+          <t>10758</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -16231,12 +16231,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -16259,12 +16259,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>52604</t>
+          <t>52668</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>57910</t>
+          <t>57890</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -16274,12 +16274,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16294,12 +16294,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>51626</t>
+          <t>51263</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>58393</t>
+          <t>58604</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16309,12 +16309,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16329,12 +16329,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>106205</t>
+          <t>106435</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>114933</t>
+          <t>114974</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16344,12 +16344,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,6%</t>
         </is>
       </c>
     </row>
@@ -16489,12 +16489,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16524,12 +16524,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>23581</t>
+          <t>23518</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16539,12 +16539,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16559,12 +16559,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>2107</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>17764</t>
+          <t>17504</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16574,12 +16574,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -16602,12 +16602,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2279</t>
+          <t>2240</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10696</t>
+          <t>11480</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16617,12 +16617,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16637,12 +16637,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1783</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>27665</t>
+          <t>27317</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16652,12 +16652,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16672,12 +16672,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3392</t>
+          <t>4178</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>30369</t>
+          <t>30675</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16687,12 +16687,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -16715,12 +16715,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>112558</t>
+          <t>111774</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>120975</t>
+          <t>121014</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16730,12 +16730,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16750,12 +16750,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>289115</t>
+          <t>289536</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>334564</t>
+          <t>334219</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16765,12 +16765,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16785,12 +16785,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>415746</t>
+          <t>416985</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>455945</t>
+          <t>454742</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16800,12 +16800,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,46%</t>
         </is>
       </c>
     </row>
@@ -16945,97 +16945,97 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>1257</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>1196</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3931</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>2,11%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="R32" s="2" t="inlineStr">
         <is>
           <t>1257</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="S32" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>4058</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>4487</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>1257</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>4399</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -17058,12 +17058,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>317</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4336</t>
+          <t>4330</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -17093,12 +17093,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>6048</t>
+          <t>5906</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>16147</t>
+          <t>15901</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -17108,12 +17108,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17128,12 +17128,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>7286</t>
+          <t>7037</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>18259</t>
+          <t>18038</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -17143,12 +17143,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -17171,12 +17171,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>142744</t>
+          <t>142750</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>146921</t>
+          <t>146763</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -17206,12 +17206,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>169051</t>
+          <t>169430</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>179642</t>
+          <t>179849</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -17221,12 +17221,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -17241,12 +17241,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>314328</t>
+          <t>313949</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>325598</t>
+          <t>325560</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -17256,12 +17256,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,55%</t>
         </is>
       </c>
     </row>
@@ -17401,12 +17401,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>4691</t>
+          <t>4720</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>13556</t>
+          <t>13120</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17416,12 +17416,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17436,12 +17436,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>21679</t>
+          <t>18716</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>51712</t>
+          <t>51530</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17451,12 +17451,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17471,12 +17471,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>31373</t>
+          <t>30422</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>60004</t>
+          <t>59125</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17486,12 +17486,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -17514,12 +17514,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>23421</t>
+          <t>23569</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>41512</t>
+          <t>41782</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17529,12 +17529,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17549,12 +17549,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>39463</t>
+          <t>37360</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>99852</t>
+          <t>99583</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17564,12 +17564,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17584,12 +17584,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>72172</t>
+          <t>71708</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>131033</t>
+          <t>130360</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17599,12 +17599,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -17627,12 +17627,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>599635</t>
+          <t>598789</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>619919</t>
+          <t>619100</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17662,12 +17662,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>885540</t>
+          <t>885913</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>974576</t>
+          <t>976059</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17677,12 +17677,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17697,12 +17697,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1498585</t>
+          <t>1499521</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1580854</t>
+          <t>1581375</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17712,12 +17712,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,94%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5404-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q5404-Provincia-trans_orig.xlsx
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5774</t>
+          <t>5696</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6370</t>
+          <t>5826</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5621</t>
+          <t>5495</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5477</t>
+          <t>4907</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>896</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7284</t>
+          <t>7415</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29765</t>
+          <t>29891</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31483</t>
+          <t>32590</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>65748</t>
+          <t>65652</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>73595</t>
+          <t>73472</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9171</t>
+          <t>10415</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>893</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>8935</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2126</t>
+          <t>2040</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12792</t>
+          <t>13448</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>992</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9091</t>
+          <t>9229</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>929</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8567</t>
+          <t>8946</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57483</t>
+          <t>56239</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>84284</t>
+          <t>84645</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>94660</t>
+          <t>95094</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>146140</t>
+          <t>146913</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>159655</t>
+          <t>159968</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,23%</t>
         </is>
       </c>
     </row>
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1167</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11167</t>
+          <t>11513</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11372</t>
+          <t>11188</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5631</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6528</t>
+          <t>6821</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>938</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8564</t>
+          <t>8370</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>45309</t>
+          <t>45758</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>69859</t>
+          <t>70109</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>80326</t>
+          <t>81187</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>119117</t>
+          <t>119649</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>131153</t>
+          <t>131108</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,51%</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4177</t>
+          <t>4777</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5341</t>
+          <t>5490</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7038</t>
+          <t>6471</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>816</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7476</t>
+          <t>6705</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>1109</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9896</t>
+          <t>10174</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3120</t>
+          <t>3126</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13473</t>
+          <t>13175</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>46462</t>
+          <t>46578</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>54277</t>
+          <t>54269</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>62430</t>
+          <t>62496</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>72132</t>
+          <t>72212</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>113613</t>
+          <t>113180</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>124760</t>
+          <t>124932</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,52%</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4796</t>
+          <t>4557</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9399</t>
+          <t>9503</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1826</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10756</t>
+          <t>10043</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>14,23%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1579</t>
+          <t>1639</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8440</t>
+          <t>8618</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10591</t>
+          <t>9210</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>4147</t>
+          <t>3735</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>14996</t>
+          <t>14652</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>20,76%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19840</t>
+          <t>19787</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27521</t>
+          <t>27565</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26572</t>
+          <t>26463</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>37183</t>
+          <t>37241</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>50097</t>
+          <t>49719</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>62752</t>
+          <t>62906</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>70,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>89,11%</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4321</t>
+          <t>4685</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>1149</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9594</t>
+          <t>9657</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1356</t>
+          <t>1166</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11398</t>
+          <t>10760</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5959</t>
+          <t>6500</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>5833</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>936</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8259</t>
+          <t>7954</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>39254</t>
+          <t>39824</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>46338</t>
+          <t>46352</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>59315</t>
+          <t>59469</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>68903</t>
+          <t>69120</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>102405</t>
+          <t>103547</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>114062</t>
+          <t>114185</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,17%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>814</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7285</t>
+          <t>7011</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t>1931</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>11121</t>
+          <t>10988</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3570</t>
+          <t>3419</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>13950</t>
+          <t>13829</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>888</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8893</t>
+          <t>7994</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7753</t>
+          <t>7317</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2396</t>
+          <t>2498</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>11962</t>
+          <t>12662</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>94487</t>
+          <t>94335</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>103241</t>
+          <t>103377</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>103303</t>
+          <t>103878</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>114202</t>
+          <t>114122</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>202333</t>
+          <t>202266</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>215875</t>
+          <t>215280</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,52%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>745</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>7259</t>
+          <t>7276</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2342</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>13647</t>
+          <t>13625</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4097</t>
+          <t>3844</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>17455</t>
+          <t>16991</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>2560</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>11502</t>
+          <t>11612</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>8452</t>
+          <t>8279</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>24223</t>
+          <t>23600</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>12912</t>
+          <t>12990</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>30907</t>
+          <t>31438</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,86%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>97191</t>
+          <t>97000</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>107684</t>
+          <t>107991</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>121600</t>
+          <t>121754</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>139877</t>
+          <t>140454</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>221915</t>
+          <t>223164</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>244613</t>
+          <t>245308</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,53%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>5392</t>
+          <t>5365</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>19218</t>
+          <t>18854</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>19259</t>
+          <t>19584</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>40464</t>
+          <t>40052</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>28782</t>
+          <t>28488</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>55118</t>
+          <t>52952</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>13308</t>
+          <t>14372</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>29910</t>
+          <t>31579</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>24356</t>
+          <t>23392</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>47509</t>
+          <t>46644</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>42763</t>
+          <t>41076</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>70900</t>
+          <t>70642</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>459469</t>
+          <t>458962</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>480326</t>
+          <t>479663</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>597520</t>
+          <t>598847</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>628825</t>
+          <t>628560</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1062788</t>
+          <t>1066793</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1102062</t>
+          <t>1104239</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,63%</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6164</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5108,12 +5108,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9139</t>
+          <t>8857</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>1156</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12006</t>
+          <t>11188</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5407</t>
+          <t>5955</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4121</t>
+          <t>3841</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14966</t>
+          <t>14506</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4121</t>
+          <t>4237</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16448</t>
+          <t>16715</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,94%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36313</t>
+          <t>35861</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43364</t>
+          <t>43408</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29898</t>
+          <t>30302</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>42592</t>
+          <t>42360</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>70546</t>
+          <t>70270</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>84496</t>
+          <t>84850</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>91,06%</t>
         </is>
       </c>
     </row>
@@ -5529,12 +5529,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13766</t>
+          <t>14083</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2293</t>
+          <t>2294</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14630</t>
+          <t>15012</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5754</t>
+          <t>6355</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>21015</t>
+          <t>22817</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>12,59%</t>
         </is>
       </c>
     </row>
@@ -5642,12 +5642,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14195</t>
+          <t>16272</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5657,12 +5657,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7256</t>
+          <t>7333</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21189</t>
+          <t>22102</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>29706</t>
+          <t>29318</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,17%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>58085</t>
+          <t>58699</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>74148</t>
+          <t>75007</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>72670</t>
+          <t>71935</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>90042</t>
+          <t>90048</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>138558</t>
+          <t>137413</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>161165</t>
+          <t>160574</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>88,57%</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>1953</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10311</t>
+          <t>10256</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4337</t>
+          <t>4334</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15357</t>
+          <t>16445</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7602</t>
+          <t>7626</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>22114</t>
+          <t>22443</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,54%</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4273</t>
+          <t>5138</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6133,12 +6133,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4126</t>
+          <t>4156</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15540</t>
+          <t>15860</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4285</t>
+          <t>4306</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17032</t>
+          <t>16320</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,03%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>44247</t>
+          <t>43743</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>52833</t>
+          <t>53671</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>54157</t>
+          <t>54160</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>68964</t>
+          <t>69970</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>102576</t>
+          <t>102364</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>119739</t>
+          <t>120524</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,81%</t>
         </is>
       </c>
     </row>
@@ -6441,12 +6441,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>952</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9207</t>
+          <t>8205</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8777</t>
+          <t>8603</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>2164</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12950</t>
+          <t>12768</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6554,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3298</t>
+          <t>3426</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14304</t>
+          <t>14837</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4561</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17065</t>
+          <t>16669</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10794</t>
+          <t>9827</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>27009</t>
+          <t>26341</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,61%</t>
         </is>
       </c>
     </row>
@@ -6667,12 +6667,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45909</t>
+          <t>45907</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>58501</t>
+          <t>58609</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6687,7 +6687,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>64656</t>
+          <t>64547</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>78814</t>
+          <t>78008</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>115219</t>
+          <t>115931</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>133843</t>
+          <t>134585</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6752,12 +6752,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,96%</t>
         </is>
       </c>
     </row>
@@ -6902,7 +6902,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5522</t>
+          <t>4832</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2869</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12325</t>
+          <t>11872</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3065</t>
+          <t>3063</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14375</t>
+          <t>14172</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6987,7 +6987,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,4%</t>
         </is>
       </c>
     </row>
@@ -7010,12 +7010,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7896</t>
+          <t>7939</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6799</t>
+          <t>6480</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2211</t>
+          <t>2091</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>12122</t>
+          <t>11397</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7095,12 +7095,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22169</t>
+          <t>22368</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30481</t>
+          <t>30502</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35483</t>
+          <t>35650</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>45733</t>
+          <t>45883</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>60636</t>
+          <t>60957</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>74406</t>
+          <t>74315</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7208,12 +7208,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,22%</t>
         </is>
       </c>
     </row>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7156</t>
+          <t>6459</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2128</t>
+          <t>2169</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10778</t>
+          <t>11784</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3229</t>
+          <t>3243</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>14026</t>
+          <t>14078</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -7471,7 +7471,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7180</t>
+          <t>6460</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>4233</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14833</t>
+          <t>15820</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5255</t>
+          <t>5240</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17794</t>
+          <t>17949</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7551,12 +7551,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,72%</t>
         </is>
       </c>
     </row>
@@ -7579,12 +7579,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>42080</t>
+          <t>42171</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>50665</t>
+          <t>50675</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>49121</t>
+          <t>49017</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>62644</t>
+          <t>61775</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>95270</t>
+          <t>95358</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>111179</t>
+          <t>110337</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>90,46%</t>
         </is>
       </c>
     </row>
@@ -7809,12 +7809,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>926</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8131</t>
+          <t>8463</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7824,12 +7824,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2989</t>
+          <t>2750</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>13886</t>
+          <t>13958</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4997</t>
+          <t>4910</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>18254</t>
+          <t>18658</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -7922,12 +7922,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>979</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8189</t>
+          <t>7809</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>9389</t>
+          <t>8272</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>24676</t>
+          <t>24668</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7972,7 +7972,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>11512</t>
+          <t>11122</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>28571</t>
+          <t>28448</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -8035,12 +8035,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>100042</t>
+          <t>99821</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>110094</t>
+          <t>110157</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>109429</t>
+          <t>108500</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>126983</t>
+          <t>127274</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>213074</t>
+          <t>213974</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>234443</t>
+          <t>235305</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8120,12 +8120,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,56%</t>
         </is>
       </c>
     </row>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t>6741</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8285,7 +8285,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2191</t>
+          <t>2123</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>12964</t>
+          <t>12263</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8315,12 +8315,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2297</t>
+          <t>2338</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>13658</t>
+          <t>13895</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8350,12 +8350,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -8378,12 +8378,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2266</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>15393</t>
+          <t>15574</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8393,12 +8393,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>4613</t>
+          <t>5419</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>18128</t>
+          <t>18247</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8428,12 +8428,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>9912</t>
+          <t>9864</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>28499</t>
+          <t>27682</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8463,12 +8463,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,71%</t>
         </is>
       </c>
     </row>
@@ -8491,12 +8491,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>104139</t>
+          <t>103765</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>117325</t>
+          <t>117425</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8506,12 +8506,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>139543</t>
+          <t>139042</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>156432</t>
+          <t>155349</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>248783</t>
+          <t>250178</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>269866</t>
+          <t>270288</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,78%</t>
         </is>
       </c>
     </row>
@@ -8721,12 +8721,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>13843</t>
+          <t>15312</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>33816</t>
+          <t>36255</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>34137</t>
+          <t>32880</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>60379</t>
+          <t>60027</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>54167</t>
+          <t>54289</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>87626</t>
+          <t>88554</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -8834,12 +8834,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>19699</t>
+          <t>18926</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>44532</t>
+          <t>43883</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8849,12 +8849,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>60606</t>
+          <t>58925</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>95705</t>
+          <t>94214</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>87021</t>
+          <t>87263</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>128747</t>
+          <t>126626</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8919,12 +8919,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,72%</t>
         </is>
       </c>
     </row>
@@ -8947,12 +8947,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>490400</t>
+          <t>488971</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>520596</t>
+          <t>520483</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8962,12 +8962,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>598491</t>
+          <t>599802</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>639661</t>
+          <t>642328</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8997,12 +8997,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1098264</t>
+          <t>1101853</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1152995</t>
+          <t>1151729</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,42%</t>
         </is>
       </c>
     </row>
@@ -9413,12 +9413,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>762</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>6473</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9137</t>
+          <t>9250</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2565</t>
+          <t>2604</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12274</t>
+          <t>12390</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -9526,12 +9526,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1596</t>
+          <t>1595</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9205</t>
+          <t>8375</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9546,7 +9546,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2453</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14410</t>
+          <t>14482</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9596,12 +9596,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>5081</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19358</t>
+          <t>18559</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,02%</t>
         </is>
       </c>
     </row>
@@ -9639,12 +9639,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26153</t>
+          <t>27766</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35649</t>
+          <t>35751</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>32314</t>
+          <t>30767</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>44736</t>
+          <t>45008</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>62,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>62524</t>
+          <t>63506</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>77736</t>
+          <t>78710</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>89,15%</t>
         </is>
       </c>
     </row>
@@ -9904,12 +9904,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10721</t>
+          <t>11586</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9924,7 +9924,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9939,12 +9939,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10814</t>
+          <t>10953</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -9982,12 +9982,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>729</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6735</t>
+          <t>7097</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10002,7 +10002,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2671</t>
+          <t>2639</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14863</t>
+          <t>13540</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10052,12 +10052,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>4205</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>17166</t>
+          <t>18282</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -10095,12 +10095,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>80560</t>
+          <t>80198</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>86563</t>
+          <t>86566</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10110,7 +10110,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>94500</t>
+          <t>95520</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>109956</t>
+          <t>109975</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>179788</t>
+          <t>179450</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>195829</t>
+          <t>195750</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,66%</t>
         </is>
       </c>
     </row>
@@ -10360,12 +10360,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12592</t>
+          <t>11974</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10395,12 +10395,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11728</t>
+          <t>11892</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10410,12 +10410,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -10438,12 +10438,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>788</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9097</t>
+          <t>8249</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10478,7 +10478,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8562</t>
+          <t>8595</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10493,7 +10493,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10508,12 +10508,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2191</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12086</t>
+          <t>12770</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10523,12 +10523,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>54449</t>
+          <t>55297</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>62686</t>
+          <t>62758</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>64707</t>
+          <t>64077</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>77420</t>
+          <t>77409</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10621,12 +10621,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>123816</t>
+          <t>124121</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>138297</t>
+          <t>137904</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10636,12 +10636,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,14%</t>
         </is>
       </c>
     </row>
@@ -10786,7 +10786,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4194</t>
+          <t>4837</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10801,7 +10801,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11134</t>
+          <t>11527</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10836,7 +10836,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>870</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13784</t>
+          <t>12397</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10866,12 +10866,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -10899,7 +10899,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7205</t>
+          <t>7112</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10929,12 +10929,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8838</t>
+          <t>9726</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2333</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12644</t>
+          <t>12935</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,28%</t>
         </is>
       </c>
     </row>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>56488</t>
+          <t>56601</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>63855</t>
+          <t>63769</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11042,12 +11042,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>76867</t>
+          <t>76645</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>89209</t>
+          <t>89200</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>136498</t>
+          <t>137182</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>151484</t>
+          <t>151679</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,05%</t>
         </is>
       </c>
     </row>
@@ -11277,7 +11277,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4710</t>
+          <t>3791</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11292,7 +11292,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4298</t>
+          <t>4628</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11327,7 +11327,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12135</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1889</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>11262</t>
+          <t>11406</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,32%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38280</t>
+          <t>38647</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>48284</t>
+          <t>48391</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>80279</t>
+          <t>80526</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>90484</t>
+          <t>90242</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,44%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1596</t>
+          <t>1646</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8954</t>
+          <t>9046</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13423</t>
+          <t>13990</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5089</t>
+          <t>5073</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>18825</t>
+          <t>18454</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>15,93%</t>
         </is>
       </c>
     </row>
@@ -11806,12 +11806,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>780</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5863</t>
+          <t>6477</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11846,7 +11846,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8616</t>
+          <t>9517</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11861,7 +11861,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2045</t>
+          <t>1607</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11015</t>
+          <t>10816</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,34%</t>
         </is>
       </c>
     </row>
@@ -11919,12 +11919,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>36086</t>
+          <t>36815</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>45139</t>
+          <t>45222</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11934,12 +11934,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11954,12 +11954,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>51763</t>
+          <t>51247</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>64760</t>
+          <t>64806</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11969,12 +11969,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11989,12 +11989,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>92041</t>
+          <t>91111</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>106797</t>
+          <t>106909</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12004,12 +12004,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,3%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>895</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7216</t>
+          <t>8411</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2544</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>14162</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4547</t>
+          <t>4391</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>18571</t>
+          <t>17302</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -12262,12 +12262,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1826</t>
+          <t>1758</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10690</t>
+          <t>10627</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>8089</t>
+          <t>8316</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>23957</t>
+          <t>24901</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>13128</t>
+          <t>13042</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>31428</t>
+          <t>31440</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12347,7 +12347,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -12375,12 +12375,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>97947</t>
+          <t>97956</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>108543</t>
+          <t>108578</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12390,12 +12390,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>113558</t>
+          <t>114351</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>133906</t>
+          <t>133576</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>216951</t>
+          <t>216991</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>238634</t>
+          <t>239174</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12460,12 +12460,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>92,06%</t>
         </is>
       </c>
     </row>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4751</t>
+          <t>4417</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12738,7 +12738,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12753,12 +12753,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2302</t>
+          <t>2341</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>13360</t>
+          <t>13324</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12768,12 +12768,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2393</t>
+          <t>2962</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>13986</t>
+          <t>15445</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -12831,7 +12831,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>129417</t>
+          <t>129751</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -12846,7 +12846,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -12866,12 +12866,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>162937</t>
+          <t>162973</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>173995</t>
+          <t>173956</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12881,12 +12881,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12901,12 +12901,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>296479</t>
+          <t>295020</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>308072</t>
+          <t>307503</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12916,12 +12916,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>5304</t>
+          <t>5197</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>17202</t>
+          <t>17404</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>18178</t>
+          <t>18566</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>42735</t>
+          <t>43157</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>26846</t>
+          <t>26693</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>54224</t>
+          <t>53192</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>13687</t>
+          <t>13897</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>30963</t>
+          <t>31637</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>35940</t>
+          <t>35638</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>67382</t>
+          <t>64932</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13244,12 +13244,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>53558</t>
+          <t>55245</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>88741</t>
+          <t>89343</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13259,12 +13259,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -13287,12 +13287,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>549165</t>
+          <t>548007</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>568723</t>
+          <t>568650</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13322,12 +13322,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>679022</t>
+          <t>679359</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>717207</t>
+          <t>717071</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1240146</t>
+          <t>1236976</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1282104</t>
+          <t>1279168</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13372,12 +13372,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,42%</t>
         </is>
       </c>
     </row>
@@ -13783,32 +13783,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3168</t>
+          <t>3399</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>1178</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6746</t>
+          <t>6719</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13818,32 +13818,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>3168</t>
+          <t>3399</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1082</t>
+          <t>1231</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6536</t>
+          <t>6958</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -13861,32 +13861,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5441</t>
+          <t>5304</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>2274</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10329</t>
+          <t>10236</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13896,32 +13896,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13740</t>
+          <t>13652</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9732</t>
+          <t>9357</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18872</t>
+          <t>18913</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13931,32 +13931,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>19181</t>
+          <t>18956</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12939</t>
+          <t>13210</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>25869</t>
+          <t>25900</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>20,52%</t>
         </is>
       </c>
     </row>
@@ -13974,32 +13974,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>50460</t>
+          <t>55651</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>45572</t>
+          <t>50719</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53588</t>
+          <t>58681</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -14009,32 +14009,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>46502</t>
+          <t>48224</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>41093</t>
+          <t>42648</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>51291</t>
+          <t>52894</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>65,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -14044,32 +14044,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>96961</t>
+          <t>103875</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>89624</t>
+          <t>97225</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>103420</t>
+          <t>110218</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>87,31%</t>
         </is>
       </c>
     </row>
@@ -14087,17 +14087,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -14122,17 +14122,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -14157,17 +14157,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -14204,7 +14204,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1690</t>
+          <t>1846</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -14214,7 +14214,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5915</t>
+          <t>6448</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -14229,7 +14229,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -14239,32 +14239,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>10817</t>
+          <t>11597</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>6907</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17665</t>
+          <t>17898</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14274,32 +14274,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>12507</t>
+          <t>13443</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7712</t>
+          <t>7853</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>19626</t>
+          <t>20859</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -14317,32 +14317,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5344</t>
+          <t>5642</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2543</t>
+          <t>1891</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10495</t>
+          <t>11270</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14352,32 +14352,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16153</t>
+          <t>17197</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11049</t>
+          <t>12149</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22439</t>
+          <t>24039</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14387,32 +14387,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>21497</t>
+          <t>22839</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>15057</t>
+          <t>15498</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>29304</t>
+          <t>31082</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,89%</t>
         </is>
       </c>
     </row>
@@ -14430,32 +14430,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>73675</t>
+          <t>80885</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>67659</t>
+          <t>75177</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>77257</t>
+          <t>85494</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14465,32 +14465,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>102022</t>
+          <t>106534</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>94534</t>
+          <t>97911</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>108874</t>
+          <t>112938</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14500,17 +14500,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>175696</t>
+          <t>187419</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>165484</t>
+          <t>177888</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>183366</t>
+          <t>196213</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14520,12 +14520,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,71%</t>
         </is>
       </c>
     </row>
@@ -14543,17 +14543,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>80709</t>
+          <t>88373</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80709</t>
+          <t>88373</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80709</t>
+          <t>88373</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -14578,17 +14578,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>128992</t>
+          <t>135328</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>128992</t>
+          <t>135328</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>128992</t>
+          <t>135328</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14613,17 +14613,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>209700</t>
+          <t>223701</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>209700</t>
+          <t>223701</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>209700</t>
+          <t>223701</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14660,32 +14660,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4248</t>
+          <t>4124</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1756</t>
+          <t>1764</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8322</t>
+          <t>8189</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14695,32 +14695,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3919</t>
+          <t>3991</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1745</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7406</t>
+          <t>7429</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14730,32 +14730,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>8167</t>
+          <t>8116</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4787</t>
+          <t>4616</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12770</t>
+          <t>13100</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,28%</t>
         </is>
       </c>
     </row>
@@ -14773,32 +14773,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3122</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1124</t>
+          <t>1456</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6599</t>
+          <t>6894</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14808,32 +14808,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7768</t>
+          <t>7779</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4657</t>
+          <t>4453</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12648</t>
+          <t>12175</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14843,32 +14843,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>10890</t>
+          <t>10916</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7236</t>
+          <t>6769</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16667</t>
+          <t>16392</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,37%</t>
         </is>
       </c>
     </row>
@@ -14886,32 +14886,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>66120</t>
+          <t>65024</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>61523</t>
+          <t>60208</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>69374</t>
+          <t>68017</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14921,32 +14921,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>75738</t>
+          <t>74079</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>69945</t>
+          <t>68767</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>79979</t>
+          <t>77888</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14956,32 +14956,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>141858</t>
+          <t>139103</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>135368</t>
+          <t>132667</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>147439</t>
+          <t>144866</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,61%</t>
         </is>
       </c>
     </row>
@@ -14999,17 +14999,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -15034,17 +15034,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>87425</t>
+          <t>85850</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>87425</t>
+          <t>85850</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>87425</t>
+          <t>85850</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -15069,17 +15069,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>160915</t>
+          <t>158135</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>160915</t>
+          <t>158135</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>160915</t>
+          <t>158135</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -15116,7 +15116,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>569</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -15126,12 +15126,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>2342</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -15151,32 +15151,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4468</t>
+          <t>4623</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2355</t>
+          <t>2418</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8081</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -15186,27 +15186,27 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>5020</t>
+          <t>5192</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>2760</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8030</t>
+          <t>8710</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -15229,32 +15229,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>4738</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>2034</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8681</t>
+          <t>9367</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15264,32 +15264,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6349</t>
+          <t>6804</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3395</t>
+          <t>3896</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9825</t>
+          <t>10202</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15299,32 +15299,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>10612</t>
+          <t>11542</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6918</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16230</t>
+          <t>16414</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -15342,32 +15342,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>69853</t>
+          <t>77849</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>65573</t>
+          <t>73057</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>72509</t>
+          <t>80597</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15377,32 +15377,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>92819</t>
+          <t>99077</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>87993</t>
+          <t>94491</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>96336</t>
+          <t>102749</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15412,32 +15412,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>162671</t>
+          <t>176926</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>156904</t>
+          <t>170758</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>167009</t>
+          <t>181973</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,97%</t>
         </is>
       </c>
     </row>
@@ -15455,17 +15455,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -15490,17 +15490,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -15525,17 +15525,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>178303</t>
+          <t>193660</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>178303</t>
+          <t>193660</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>178303</t>
+          <t>193660</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -15607,32 +15607,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1207</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>386</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3322</t>
+          <t>3631</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15642,32 +15642,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1207</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>386</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>3631</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -15685,32 +15685,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3994</t>
+          <t>4063</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7661</t>
+          <t>7611</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15720,32 +15720,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7862</t>
+          <t>8164</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>5069</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11302</t>
+          <t>11838</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15755,32 +15755,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>11856</t>
+          <t>12227</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>8525</t>
+          <t>8202</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>16361</t>
+          <t>16757</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,09%</t>
         </is>
       </c>
     </row>
@@ -15798,32 +15798,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>30822</t>
+          <t>32440</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27155</t>
+          <t>28892</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32862</t>
+          <t>34494</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15833,32 +15833,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>50177</t>
+          <t>52103</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>46075</t>
+          <t>48035</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>53050</t>
+          <t>55233</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15868,32 +15868,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>80999</t>
+          <t>84542</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>76197</t>
+          <t>80012</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>84526</t>
+          <t>88880</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>90,65%</t>
         </is>
       </c>
     </row>
@@ -15911,17 +15911,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15946,17 +15946,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>59246</t>
+          <t>61542</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>59246</t>
+          <t>61542</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>59246</t>
+          <t>61542</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15981,17 +15981,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>94062</t>
+          <t>98045</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>94062</t>
+          <t>98045</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>94062</t>
+          <t>98045</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -16028,32 +16028,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>1937</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>699</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4476</t>
+          <t>4221</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -16063,32 +16063,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5132</t>
+          <t>5283</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2815</t>
+          <t>3109</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8061</t>
+          <t>8567</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -16098,22 +16098,22 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>7036</t>
+          <t>7221</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4421</t>
+          <t>4492</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10740</t>
+          <t>10759</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
@@ -16123,7 +16123,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,44%</t>
         </is>
       </c>
     </row>
@@ -16141,32 +16141,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2512</t>
+          <t>2547</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>848</t>
+          <t>910</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -16176,32 +16176,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>4834</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2739</t>
+          <t>2918</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7995</t>
+          <t>7799</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -16211,32 +16211,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>7346</t>
+          <t>7484</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4586</t>
+          <t>4912</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10758</t>
+          <t>11716</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -16254,32 +16254,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>55845</t>
+          <t>55740</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>52668</t>
+          <t>52772</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>57890</t>
+          <t>58009</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16289,32 +16289,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>55292</t>
+          <t>57088</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>51263</t>
+          <t>52942</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>58604</t>
+          <t>60300</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16324,32 +16324,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>111137</t>
+          <t>112827</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>106435</t>
+          <t>107641</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>114974</t>
+          <t>116938</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,69%</t>
         </is>
       </c>
     </row>
@@ -16367,17 +16367,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -16402,17 +16402,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>65258</t>
+          <t>67309</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>65258</t>
+          <t>67309</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>65258</t>
+          <t>67309</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -16437,17 +16437,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>125519</t>
+          <t>127532</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>125519</t>
+          <t>127532</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>125519</t>
+          <t>127532</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -16519,32 +16519,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>7962</t>
+          <t>9301</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>4726</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>23518</t>
+          <t>15922</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16554,32 +16554,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>7962</t>
+          <t>9301</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>5163</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>17504</t>
+          <t>15732</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -16597,32 +16597,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>5507</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2240</t>
+          <t>2864</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11480</t>
+          <t>12729</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16632,32 +16632,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>9361</t>
+          <t>12113</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2259</t>
+          <t>7410</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>27317</t>
+          <t>18176</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16667,32 +16667,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>14868</t>
+          <t>18929</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4178</t>
+          <t>12430</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>30675</t>
+          <t>27009</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -16710,32 +16710,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>117747</t>
+          <t>144525</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>111774</t>
+          <t>138612</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>121014</t>
+          <t>148477</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16745,32 +16745,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>321266</t>
+          <t>142710</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>289536</t>
+          <t>134478</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>334219</t>
+          <t>149227</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16780,32 +16780,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>439014</t>
+          <t>287235</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>416985</t>
+          <t>277862</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>454742</t>
+          <t>295171</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>93,57%</t>
         </is>
       </c>
     </row>
@@ -16823,17 +16823,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>151341</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>151341</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>151341</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -16858,17 +16858,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>338589</t>
+          <t>164124</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>338589</t>
+          <t>164124</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>338589</t>
+          <t>164124</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -16893,17 +16893,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>461844</t>
+          <t>315465</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>461844</t>
+          <t>315465</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>461844</t>
+          <t>315465</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -16975,7 +16975,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -16985,12 +16985,12 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3931</t>
+          <t>4825</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -17000,7 +17000,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -17010,7 +17010,7 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
@@ -17020,12 +17020,12 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4487</t>
+          <t>5577</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
@@ -17035,7 +17035,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -17053,32 +17053,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>657</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4330</t>
+          <t>5309</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -17088,32 +17088,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>10127</t>
+          <t>12099</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>5906</t>
+          <t>7609</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>15901</t>
+          <t>19178</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17123,32 +17123,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>11527</t>
+          <t>14094</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>7037</t>
+          <t>8516</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>18038</t>
+          <t>22058</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -17166,32 +17166,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>145681</t>
+          <t>161559</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>142750</t>
+          <t>158245</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>146763</t>
+          <t>162897</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -17201,32 +17201,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>175258</t>
+          <t>199153</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>169430</t>
+          <t>191745</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>179849</t>
+          <t>204304</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -17236,32 +17236,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>320939</t>
+          <t>360713</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>313949</t>
+          <t>352860</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>325560</t>
+          <t>366654</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,43%</t>
         </is>
       </c>
     </row>
@@ -17279,17 +17279,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>147080</t>
+          <t>163554</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>147080</t>
+          <t>163554</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>147080</t>
+          <t>163554</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -17314,17 +17314,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>186642</t>
+          <t>212766</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>186642</t>
+          <t>212766</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>186642</t>
+          <t>212766</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -17349,17 +17349,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>333722</t>
+          <t>376321</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>333722</t>
+          <t>376321</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>333722</t>
+          <t>376321</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -17396,32 +17396,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>8394</t>
+          <t>8477</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>4720</t>
+          <t>4957</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>13120</t>
+          <t>13978</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17431,32 +17431,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>37930</t>
+          <t>40984</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>18716</t>
+          <t>32125</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>51530</t>
+          <t>51194</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17466,32 +17466,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>46324</t>
+          <t>49461</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>30422</t>
+          <t>39688</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>59125</t>
+          <t>60330</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -17509,32 +17509,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>31582</t>
+          <t>34242</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>23569</t>
+          <t>25678</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>41782</t>
+          <t>45234</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17544,32 +17544,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>76194</t>
+          <t>82746</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>37360</t>
+          <t>69870</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>99583</t>
+          <t>97847</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17579,32 +17579,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>107776</t>
+          <t>116988</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>71708</t>
+          <t>102093</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>130360</t>
+          <t>133945</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -17622,32 +17622,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>610202</t>
+          <t>673672</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>598789</t>
+          <t>661824</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>619100</t>
+          <t>683371</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17657,32 +17657,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>919073</t>
+          <t>778968</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>885913</t>
+          <t>762906</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>976059</t>
+          <t>794829</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17692,32 +17692,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1529275</t>
+          <t>1452640</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1499521</t>
+          <t>1433359</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1581375</t>
+          <t>1470580</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>90,83%</t>
         </is>
       </c>
     </row>
@@ -17735,17 +17735,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -17770,17 +17770,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>1033197</t>
+          <t>902698</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1033197</t>
+          <t>902698</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>1033197</t>
+          <t>902698</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -17805,17 +17805,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1683375</t>
+          <t>1619089</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1683375</t>
+          <t>1619089</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1683375</t>
+          <t>1619089</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
